--- a/Cosas que llegan de mercado/2026/Periodo 1/Nota3.xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/Nota3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF6093C-BD69-4096-B1E0-C09B7082A950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459F11CE-BB2B-44D1-B65B-2D9C928E35F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
